--- a/timesheets_final.xlsx
+++ b/timesheets_final.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -675,6 +675,190 @@
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Jake Williams</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>123 Oak Street Residence</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jake Williams</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>456 Pine Road - Smith Property</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jake Williams</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>123 Oak Street Residence</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Jake Williams</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>456 Pine Road - Smith Property</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Jake Williams</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>123 Oak Street Residence</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Jake Williams</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>456 Pine Road - Smith Property</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Jake Williams</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>123 Oak Street Residence</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Jake Williams</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>04/28/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>456 Pine Road - Smith Property</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/timesheets_final.xlsx
+++ b/timesheets_final.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="9960" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,9 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -47,10 +45,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -424,6 +420,7 @@
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,6 +449,11 @@
           <t>Hours</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date Submitted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -459,8 +461,10 @@
           <t>Jake Williams</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>46140</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>04/28/2026</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -480,8 +484,10 @@
           <t>Jake Williams</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>46140</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>04/28/2026</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -503,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>04-28-2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -526,7 +532,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>04-28-2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,6 +569,11 @@
       <c r="E6" t="n">
         <v>4</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>06/06/2026 03:49 PM</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -586,6 +597,11 @@
       <c r="E7" t="n">
         <v>5</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>06/06/2026 03:49 PM</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -593,8 +609,10 @@
           <t>Jake Williams</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>46140</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>04/28/2026</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -607,6 +625,11 @@
       <c r="E8" t="n">
         <v>4</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>06/29/2026 08:38 PM</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -614,8 +637,10 @@
           <t>Jake Williams</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>46140</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>04/28/2026</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -628,235 +653,10 @@
       <c r="E9" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Jake Williams</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>123 Oak Street Residence</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Jake Williams</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>456 Pine Road - Smith Property</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Jake Williams</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>123 Oak Street Residence</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Jake Williams</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>456 Pine Road - Smith Property</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Jake Williams</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>123 Oak Street Residence</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Jake Williams</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>456 Pine Road - Smith Property</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Jake Williams</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>123 Oak Street Residence</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Jake Williams</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>456 Pine Road - Smith Property</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Jake Williams</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>123 Oak Street Residence</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Jake Williams</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>456 Pine Road - Smith Property</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>06/29/2026 08:38 PM</t>
+        </is>
       </c>
     </row>
   </sheetData>
